--- a/excel/roleLevel.xlsx
+++ b/excel/roleLevel.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="88">
   <si>
     <t>编号</t>
   </si>
@@ -70,7 +70,10 @@
     <t>主动描述</t>
   </si>
   <si>
-    <t>升级描述</t>
+    <t>被动升级描述</t>
+  </si>
+  <si>
+    <t>主动升级描述</t>
   </si>
   <si>
     <t>升级材料</t>
@@ -112,7 +115,10 @@
     <t>initiativeDesc</t>
   </si>
   <si>
-    <t>upgradeDesc</t>
+    <t>passiveUpgradeDesc</t>
+  </si>
+  <si>
+    <t>initiativeUpgradeDesc</t>
   </si>
   <si>
     <t>upgradeItem</t>
@@ -136,6 +142,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：50s。</t>
   </si>
   <si>
+    <t>技能冷却15s-&gt;16s</t>
+  </si>
+  <si>
     <t>技能冷却50s-&gt;51s</t>
   </si>
   <si>
@@ -148,6 +157,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：51s。</t>
   </si>
   <si>
+    <t>技能冷却16s-&gt;17s</t>
+  </si>
+  <si>
     <t>技能冷却51s-&gt;52s</t>
   </si>
   <si>
@@ -160,6 +172,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：52s。</t>
   </si>
   <si>
+    <t>技能冷却17s-&gt;18s</t>
+  </si>
+  <si>
     <t>技能冷却52s-&gt;53s</t>
   </si>
   <si>
@@ -172,6 +187,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：53s。</t>
   </si>
   <si>
+    <t>技能冷却18s-&gt;19s</t>
+  </si>
+  <si>
     <t>技能冷却53s-&gt;54s</t>
   </si>
   <si>
@@ -184,6 +202,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：54s。</t>
   </si>
   <si>
+    <t>技能冷却19s-&gt;20s</t>
+  </si>
+  <si>
     <t>技能冷却54s-&gt;55s</t>
   </si>
   <si>
@@ -196,6 +217,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：55s。</t>
   </si>
   <si>
+    <t>技能冷却20s-&gt;21s</t>
+  </si>
+  <si>
     <t>技能冷却55s-&gt;56s</t>
   </si>
   <si>
@@ -208,6 +232,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：56s。</t>
   </si>
   <si>
+    <t>技能冷却21s-&gt;22s</t>
+  </si>
+  <si>
     <t>技能冷却56s-&gt;57s</t>
   </si>
   <si>
@@ -220,6 +247,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：57s。</t>
   </si>
   <si>
+    <t>技能冷却22s-&gt;23s</t>
+  </si>
+  <si>
     <t>技能冷却57s-&gt;58s</t>
   </si>
   <si>
@@ -230,6 +260,9 @@
   </si>
   <si>
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：58s。</t>
+  </si>
+  <si>
+    <t>技能冷却23s-&gt;24s</t>
   </si>
   <si>
     <t>技能冷却58s-&gt;59s</t>
@@ -1244,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N617"/>
+  <dimension ref="A1:O617"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="25.125" style="2" customWidth="1"/>
@@ -1252,13 +1285,14 @@
     <col min="9" max="9" width="21.5166666666667" style="2" customWidth="1"/>
     <col min="10" max="10" width="93.8" style="2" customWidth="1"/>
     <col min="11" max="11" width="105.316666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="38.475" style="2" customWidth="1"/>
-    <col min="13" max="13" width="29.45" style="2" customWidth="1"/>
-    <col min="14" max="14" width="18.2583333333333" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="23.0416666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="38.475" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.45" style="2" customWidth="1"/>
+    <col min="15" max="15" width="18.2583333333333" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:14">
+    <row r="1" ht="16.5" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1301,96 +1335,105 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:14">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:14">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+        <v>31</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="A4" s="4">
         <v>0</v>
       </c>
@@ -1411,25 +1454,28 @@
         <v>50</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="1">
+        <v>36</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="1">
         <v>100000</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1449,25 +1495,28 @@
         <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="1">
+        <v>41</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="1">
         <v>200000</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1487,25 +1536,28 @@
         <v>52</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="1">
+        <v>46</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="1">
         <v>300000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -1525,25 +1577,28 @@
         <v>53</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="1">
+        <v>51</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="1">
         <v>400000</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -1563,25 +1618,28 @@
         <v>54</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="1">
+        <v>56</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="1">
         <v>500000</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
+    <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -1601,25 +1659,28 @@
         <v>55</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="1">
+        <v>61</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="1">
         <v>600000</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
+    <row r="10" s="1" customFormat="1" spans="1:15">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -1639,25 +1700,28 @@
         <v>56</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="1">
+        <v>66</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="1">
         <v>700000</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
+    <row r="11" s="1" customFormat="1" spans="1:15">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -1677,25 +1741,28 @@
         <v>57</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="1">
+        <v>71</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="1">
         <v>800000</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
+    <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1715,25 +1782,28 @@
         <v>58</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="1">
+        <v>76</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" s="1">
         <v>900000</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
+    <row r="13" s="1" customFormat="1" spans="1:15">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1753,19 +1823,22 @@
         <v>59</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
+        <v>80</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:15">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1785,16 +1858,16 @@
         <v>40</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:15">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1814,13 +1887,13 @@
         <v>30</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -1837,10 +1910,10 @@
         <v>35</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:11">
@@ -1863,13 +1936,13 @@
         <v>50</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:11">
@@ -1892,13 +1965,13 @@
         <v>40</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:11">
@@ -1921,10 +1994,10 @@
         <v>30</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:11">
@@ -1944,10 +2017,10 @@
         <v>35</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:11">
@@ -1970,13 +2043,13 @@
         <v>50</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:11">
@@ -1999,13 +2072,13 @@
         <v>40</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:11">
@@ -2028,10 +2101,10 @@
         <v>30</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:11">
@@ -2051,10 +2124,10 @@
         <v>35</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:11">

--- a/excel/roleLevel.xlsx
+++ b/excel/roleLevel.xlsx
@@ -1817,7 +1817,7 @@
         <v>24</v>
       </c>
       <c r="G13" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H13" s="1">
         <v>59</v>

--- a/excel/roleLevel.xlsx
+++ b/excel/roleLevel.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
         <v>16</v>
@@ -1527,7 +1527,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <v>17</v>
@@ -1568,7 +1568,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>18</v>
@@ -1609,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
         <v>19</v>
@@ -1650,7 +1650,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <v>20</v>
@@ -1691,7 +1691,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="1">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
         <v>21</v>
@@ -1732,7 +1732,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
         <v>22</v>
@@ -1773,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="1">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
         <v>23</v>
@@ -1814,7 +1814,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="1">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
         <v>34</v>
